--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="53">
   <si>
     <t>Result</t>
   </si>
@@ -186,6 +186,15 @@
   </si>
   <si>
     <t>Thu Jul 09 16:15:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:45:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:45:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:46:35 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -656,7 +665,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -671,7 +680,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>16</v>
@@ -689,7 +698,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
